--- a/BinancePTF/Trade History Reconstructed.xlsx
+++ b/BinancePTF/Trade History Reconstructed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Desktop\Jupyter\Projets\Risk Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Jupyter\Projets\Risk Management\BinancePTF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011F3170-5A6B-4D0A-8625-DC9E3CBE777A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C252A2BF-F330-41B8-8460-CB67093B83FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="70">
   <si>
     <t>Date(UTC)</t>
   </si>
@@ -231,16 +231,13 @@
   <si>
     <t>UMAEUR</t>
   </si>
-  <si>
-    <t>BNDUSDT</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -254,6 +251,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -296,7 +294,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -602,13 +600,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L177"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -646,7 +644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>46301.65724537037</v>
       </c>
@@ -672,7 +670,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46301.65724537037</v>
       </c>
@@ -698,7 +696,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46301.657002314816</v>
       </c>
@@ -724,12 +722,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46301.632650462961</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -750,7 +748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>46298.635416666657</v>
       </c>
@@ -788,7 +786,7 @@
         <v>1.9892170000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>46298.632650462961</v>
       </c>
@@ -826,7 +824,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>46298.63144675926</v>
       </c>
@@ -864,7 +862,7 @@
         <v>1.48E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>46298.629965277767</v>
       </c>
@@ -902,7 +900,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46273.46</v>
       </c>
@@ -940,7 +938,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>46262.504317129627</v>
       </c>
@@ -978,7 +976,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>46273.46</v>
       </c>
@@ -1016,7 +1014,7 @@
         <v>245.4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>46254.079594907409</v>
       </c>
@@ -1054,7 +1052,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>46203.843715277777</v>
       </c>
@@ -1092,7 +1090,7 @@
         <v>858.7</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>46203.842511574083</v>
       </c>
@@ -1130,7 +1128,7 @@
         <v>719.00000000000011</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>46203.842372685183</v>
       </c>
@@ -1168,7 +1166,7 @@
         <v>0.252</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>46173.874039351853</v>
       </c>
@@ -1206,7 +1204,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>46173.87358796296</v>
       </c>
@@ -1244,7 +1242,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>46173.873171296298</v>
       </c>
@@ -1282,7 +1280,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>46173.872395833343</v>
       </c>
@@ -1320,7 +1318,7 @@
         <v>425.10000000000008</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>46173.870856481481</v>
       </c>
@@ -1358,7 +1356,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>46173.870856481481</v>
       </c>
@@ -1396,7 +1394,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>46173.870706018519</v>
       </c>
@@ -1434,7 +1432,7 @@
         <v>0.63300000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>46173.870462962957</v>
       </c>
@@ -1472,7 +1470,7 @@
         <v>0.38800000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>46173.870462962957</v>
       </c>
@@ -1510,7 +1508,7 @@
         <v>0.33900000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>46143.530752314808</v>
       </c>
@@ -1548,7 +1546,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>46143.53056712963</v>
       </c>
@@ -1586,7 +1584,7 @@
         <v>0.63400000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>46143.530150462961</v>
       </c>
@@ -1624,7 +1622,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>46143.529085648152</v>
       </c>
@@ -1662,7 +1660,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>46143.529085648152</v>
       </c>
@@ -1700,7 +1698,7 @@
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>46143.529085648152</v>
       </c>
@@ -1738,7 +1736,7 @@
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>46143.52851851852</v>
       </c>
@@ -1776,7 +1774,7 @@
         <v>184.1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>46143.52815972222</v>
       </c>
@@ -1814,7 +1812,7 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>46113.60832175926</v>
       </c>
@@ -1852,7 +1850,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>46113.608113425929</v>
       </c>
@@ -1890,7 +1888,7 @@
         <v>0.70699999999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>46113.607094907413</v>
       </c>
@@ -1928,7 +1926,7 @@
         <v>1584.7</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>46081.500879629632</v>
       </c>
@@ -1966,7 +1964,7 @@
         <v>1702.7</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>46081.500462962962</v>
       </c>
@@ -2004,7 +2002,7 @@
         <v>4.6000000000000001E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>46081.5003125</v>
       </c>
@@ -2042,7 +2040,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>46054.616527777784</v>
       </c>
@@ -2080,7 +2078,7 @@
         <v>0.63600000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>46054.61582175926</v>
       </c>
@@ -2118,7 +2116,7 @@
         <v>1.14E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>46054.615127314813</v>
       </c>
@@ -2156,7 +2154,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>46023.116932870369</v>
       </c>
@@ -2194,7 +2192,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>46023.116550925923</v>
       </c>
@@ -2232,7 +2230,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>46023.116550925923</v>
       </c>
@@ -2270,7 +2268,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>46023.116550925923</v>
       </c>
@@ -2308,7 +2306,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46023.11582175926</v>
       </c>
@@ -2346,7 +2344,7 @@
         <v>5.5000000000000003E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>45990.61078703704</v>
       </c>
@@ -2384,7 +2382,7 @@
         <v>245.1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>45990.610358796293</v>
       </c>
@@ -2422,7 +2420,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>45990.609155092592</v>
       </c>
@@ -2460,7 +2458,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>45962.060810185183</v>
       </c>
@@ -2498,7 +2496,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>45962.059664351851</v>
       </c>
@@ -2536,7 +2534,7 @@
         <v>2624.2</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>45962.059664351851</v>
       </c>
@@ -2574,7 +2572,7 @@
         <v>585.20000000000005</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>45962.059027777781</v>
       </c>
@@ -2612,7 +2610,7 @@
         <v>1.0019999999999999E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>45931.030428240738</v>
       </c>
@@ -2650,7 +2648,7 @@
         <v>3.96E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>45931.029803240737</v>
       </c>
@@ -2688,7 +2686,7 @@
         <v>905.7</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>45931.028958333343</v>
       </c>
@@ -2726,7 +2724,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>45900.939155092587</v>
       </c>
@@ -2764,7 +2762,7 @@
         <v>200.6</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>45900.938969907409</v>
       </c>
@@ -2802,7 +2800,7 @@
         <v>6.3000000000000003E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>45900.936724537038</v>
       </c>
@@ -2840,7 +2838,7 @@
         <v>2022.6</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>45900.936018518521</v>
       </c>
@@ -2878,7 +2876,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>45900.935787037037</v>
       </c>
@@ -2916,7 +2914,7 @@
         <v>6.93E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>45900.935324074067</v>
       </c>
@@ -2954,7 +2952,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>45891.845937500002</v>
       </c>
@@ -2992,7 +2990,7 @@
         <v>1.648052154152757E-5</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>45891.845937500002</v>
       </c>
@@ -3030,7 +3028,7 @@
         <v>0.56455222362371316</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>45891.845937500002</v>
       </c>
@@ -3068,7 +3066,7 @@
         <v>0.90185245368865785</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>45891.845937500002</v>
       </c>
@@ -3106,7 +3104,7 @@
         <v>2.229999999999999E-6</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>45891.845937500002</v>
       </c>
@@ -3144,7 +3142,7 @@
         <v>1.21952E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>45891.845937500002</v>
       </c>
@@ -3182,7 +3180,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>45891.845937500002</v>
       </c>
@@ -3220,7 +3218,7 @@
         <v>2.5209054507969599E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>45891.844282407408</v>
       </c>
@@ -3258,7 +3256,7 @@
         <v>8718.1239999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>45891.844282407408</v>
       </c>
@@ -3296,7 +3294,7 @@
         <v>586.99999999999989</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>45891.843576388892</v>
       </c>
@@ -3334,7 +3332,7 @@
         <v>8724.1440000000021</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>45891.843576388892</v>
       </c>
@@ -3372,7 +3370,7 @@
         <v>12792</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>45878.026342592602</v>
       </c>
@@ -3410,7 +3408,7 @@
         <v>1.8984839999999999E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>45878.026342592602</v>
       </c>
@@ -3448,7 +3446,7 @@
         <v>116.4</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>45560.642766203702</v>
       </c>
@@ -3486,7 +3484,7 @@
         <v>56.999999999999993</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>45560.642766203702</v>
       </c>
@@ -3524,7 +3522,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>45560.642766203702</v>
       </c>
@@ -3562,7 +3560,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>45560.642361111109</v>
       </c>
@@ -3600,7 +3598,7 @@
         <v>1456.1</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>45553.906388888892</v>
       </c>
@@ -3638,7 +3636,7 @@
         <v>1.3220300000000001E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>45553.906388888892</v>
       </c>
@@ -3676,7 +3674,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>45529.90896990741</v>
       </c>
@@ -3714,7 +3712,7 @@
         <v>2.5412999999999998E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>45529.90896990741</v>
       </c>
@@ -3752,7 +3750,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>45529.906527777777</v>
       </c>
@@ -3790,7 +3788,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>45529.906145833331</v>
       </c>
@@ -3828,7 +3826,7 @@
         <v>218.6</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>45528.998402777783</v>
       </c>
@@ -3866,7 +3864,7 @@
         <v>0.1015056</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>45528.998402777783</v>
       </c>
@@ -3904,7 +3902,7 @@
         <v>370.99999999999989</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>45500.560335648152</v>
       </c>
@@ -3942,7 +3940,7 @@
         <v>3.1043999999999999E-4</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>45500.560335648152</v>
       </c>
@@ -3980,7 +3978,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>45500.559224537043</v>
       </c>
@@ -4018,7 +4016,7 @@
         <v>2.7748800000000011E-4</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>45500.559224537043</v>
       </c>
@@ -4056,7 +4054,7 @@
         <v>7.1999999999999989E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>45500.559224537043</v>
       </c>
@@ -4094,7 +4092,7 @@
         <v>1.4529580000000001E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>45500.559224537043</v>
       </c>
@@ -4132,7 +4130,7 @@
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>45488.037268518521</v>
       </c>
@@ -4170,7 +4168,7 @@
         <v>194.71378021999999</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>45479.777083333327</v>
       </c>
@@ -4208,7 +4206,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>45479.76871527778</v>
       </c>
@@ -4246,7 +4244,7 @@
         <v>85.59999999999998</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>45479.768495370372</v>
       </c>
@@ -4284,7 +4282,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>45479.673125000001</v>
       </c>
@@ -4322,7 +4320,7 @@
         <v>1976.8</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>45479.672395833331</v>
       </c>
@@ -4360,7 +4358,7 @@
         <v>5181574</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>45459.611851851849</v>
       </c>
@@ -4398,7 +4396,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>45457.954826388886</v>
       </c>
@@ -4436,7 +4434,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>45457.954826388886</v>
       </c>
@@ -4474,7 +4472,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>45457.954560185193</v>
       </c>
@@ -4512,7 +4510,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>45457.954560185193</v>
       </c>
@@ -4550,7 +4548,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>45457.95416666667</v>
       </c>
@@ -4588,7 +4586,7 @@
         <v>1746724</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>45455.630983796298</v>
       </c>
@@ -4626,7 +4624,7 @@
         <v>3465.2</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>45455.630624999998</v>
       </c>
@@ -4664,7 +4662,7 @@
         <v>1.8799999999999999E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>45455.036585648151</v>
       </c>
@@ -4702,7 +4700,7 @@
         <v>1.384E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>45455.036585648151</v>
       </c>
@@ -4740,7 +4738,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -4778,7 +4776,7 @@
         <v>1.2520929999999999E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -4816,7 +4814,7 @@
         <v>0.127</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -4854,7 +4852,7 @@
         <v>2.9577000000000002E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -4892,7 +4890,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -4930,7 +4928,7 @@
         <v>2.4647499999999991E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -4968,7 +4966,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -5006,7 +5004,7 @@
         <v>4.929499999999999E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -5044,7 +5042,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -5082,7 +5080,7 @@
         <v>8.0843799999999997E-4</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>45451.519849537042</v>
       </c>
@@ -5120,7 +5118,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>45451.519594907397</v>
       </c>
@@ -5158,7 +5156,7 @@
         <v>1.121</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>45451.519594907397</v>
       </c>
@@ -5196,7 +5194,7 @@
         <v>1.105306E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>45451.504004629627</v>
       </c>
@@ -5234,7 +5232,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>45450.922071759262</v>
       </c>
@@ -5272,7 +5270,7 @@
         <v>1210.5</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>45450.922071759262</v>
       </c>
@@ -5310,7 +5308,7 @@
         <v>1082.2</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>45450.921388888892</v>
       </c>
@@ -5348,7 +5346,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>45450.920393518521</v>
       </c>
@@ -5386,7 +5384,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>45447.972905092603</v>
       </c>
@@ -5424,7 +5422,7 @@
         <v>5.1688999999999999E-5</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>45447.972905092603</v>
       </c>
@@ -5462,7 +5460,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>45447.949826388889</v>
       </c>
@@ -5500,7 +5498,7 @@
         <v>2.4904700000000012E-4</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>45447.949826388889</v>
       </c>
@@ -5538,7 +5536,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>45446.501504629632</v>
       </c>
@@ -5576,7 +5574,7 @@
         <v>1.363E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>45446.501504629632</v>
       </c>
@@ -5614,7 +5612,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>45446.496493055558</v>
       </c>
@@ -5652,7 +5650,7 @@
         <v>6.9092000000000003E-4</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>45446.496493055558</v>
       </c>
@@ -5690,7 +5688,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>45446.420810185176</v>
       </c>
@@ -5728,7 +5726,7 @@
         <v>6.6420899999999991E-4</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>45446.420810185176</v>
       </c>
@@ -5766,7 +5764,7 @@
         <v>6.2999999999999989</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>45442.009212962963</v>
       </c>
@@ -5804,7 +5802,7 @@
         <v>9.3258000000000002E-4</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>45442.009212962963</v>
       </c>
@@ -5842,7 +5840,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>45441.908472222232</v>
       </c>
@@ -5880,7 +5878,7 @@
         <v>7.3358999999999989E-4</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>45441.908472222232</v>
       </c>
@@ -5918,7 +5916,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>45440.886192129627</v>
       </c>
@@ -5956,7 +5954,7 @@
         <v>7.6406E-4</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>45439.966828703713</v>
       </c>
@@ -5994,7 +5992,7 @@
         <v>4.0046400000000012E-4</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>45439.966828703713</v>
       </c>
@@ -6032,7 +6030,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>45439.965474537043</v>
       </c>
@@ -6070,7 +6068,7 @@
         <v>2.31E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>45439.965474537043</v>
       </c>
@@ -6108,7 +6106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>45438.413587962961</v>
       </c>
@@ -6146,7 +6144,7 @@
         <v>3.02637E-3</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>45438.066701388889</v>
       </c>
@@ -6184,7 +6182,7 @@
         <v>3.3587014499999999</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>45438.064282407409</v>
       </c>
@@ -6222,7 +6220,7 @@
         <v>4.5792935400000001</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>45438.062881944446</v>
       </c>
@@ -6260,7 +6258,7 @@
         <v>4804.5860693499999</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>45438.016701388893</v>
       </c>
@@ -6298,7 +6296,7 @@
         <v>288.7121952</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>45438.011793981481</v>
       </c>
@@ -6336,7 +6334,7 @@
         <v>192.84638819</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>45437.934502314813</v>
       </c>
@@ -6374,7 +6372,7 @@
         <v>6928298.2400000002</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>45437.927314814813</v>
       </c>
@@ -6412,7 +6410,7 @@
         <v>12.848380199999999</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>45436.947754629633</v>
       </c>
@@ -6450,7 +6448,7 @@
         <v>3.8117280000000003E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>45436.935613425929</v>
       </c>
@@ -6488,7 +6486,7 @@
         <v>4.1975459999999999E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>45436.934664351851</v>
       </c>
@@ -6526,7 +6524,7 @@
         <v>0.62376507000000003</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>45436.433229166672</v>
       </c>
@@ -6564,7 +6562,7 @@
         <v>1.5554799999999999E-3</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>45426.641608796293</v>
       </c>
@@ -6602,7 +6600,7 @@
         <v>8.4584000000000005E-4</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>45425.858472222222</v>
       </c>
@@ -6640,7 +6638,7 @@
         <v>0.69880220999999998</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>45422.839930555558</v>
       </c>
@@ -6678,7 +6676,7 @@
         <v>1.85240322</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>45422.83865740741</v>
       </c>
@@ -6716,7 +6714,7 @@
         <v>5.3372899999999997E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>45422.837546296287</v>
       </c>
@@ -6754,7 +6752,7 @@
         <v>5.1197000000000005E-4</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>45422.835844907408</v>
       </c>
@@ -6792,7 +6790,7 @@
         <v>6.9800216099999997</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>45422.833622685182</v>
       </c>
@@ -6830,7 +6828,7 @@
         <v>163.24640485</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>45422.831307870372</v>
       </c>
@@ -6868,7 +6866,7 @@
         <v>0.13982043</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>45422.829675925917</v>
       </c>
@@ -6906,7 +6904,7 @@
         <v>18.365145070000001</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>45422.08221064815</v>
       </c>
@@ -6944,7 +6942,7 @@
         <v>0.13634721999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>45422.07099537037</v>
       </c>
@@ -6982,7 +6980,7 @@
         <v>26.088272459999999</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>45422.069872685177</v>
       </c>
@@ -7020,7 +7018,7 @@
         <v>6.828869999999999E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>45422.056192129632</v>
       </c>
@@ -7058,7 +7056,7 @@
         <v>11.426821869999999</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>45422.018043981479</v>
       </c>
@@ -7096,7 +7094,7 @@
         <v>2.3929421799999999</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>45421.93954861111</v>
       </c>
@@ -7134,7 +7132,7 @@
         <v>205.82814242000001</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>45421.817245370366</v>
       </c>
@@ -7172,7 +7170,7 @@
         <v>6.4388078499999999</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>45418.977210648147</v>
       </c>
@@ -7210,7 +7208,7 @@
         <v>8.4072299999999999E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>45418.969189814823</v>
       </c>
@@ -7248,7 +7246,7 @@
         <v>4.0884999999999999E-4</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>45414.950277777767</v>
       </c>

--- a/BinancePTF/Trade History Reconstructed.xlsx
+++ b/BinancePTF/Trade History Reconstructed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/BinancePTF/Trade History Reconstructed.xlsx
+++ b/BinancePTF/Trade History Reconstructed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
